--- a/accountant-skill/data/output/Feb2025/financial_statements_Feb2025.xlsx
+++ b/accountant-skill/data/output/Feb2025/financial_statements_Feb2025.xlsx
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-24506835.22</v>
+        <v>1245164.779999999</v>
       </c>
     </row>
     <row r="9">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>-25192501.89</v>
+        <v>559498.1099999993</v>
       </c>
     </row>
     <row r="12">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-25192501.89</v>
+        <v>559498.1099999993</v>
       </c>
     </row>
   </sheetData>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -706,23 +706,33 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>559498.1099999993</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>TOTAL EQUITY</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
-        <v>400000000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="B23" s="4" t="n">
+        <v>400559498.11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>TOTAL LIABILITIES &amp; EQUITY</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>400000000</v>
+      <c r="B25" s="4" t="n">
+        <v>400559498.11</v>
       </c>
     </row>
   </sheetData>

--- a/accountant-skill/data/output/Feb2025/financial_statements_Feb2025.xlsx
+++ b/accountant-skill/data/output/Feb2025/financial_statements_Feb2025.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,8 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);-"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,16 +40,46 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -54,11 +87,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <bottom style="double"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -66,6 +111,25 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,80 +492,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Income Statement</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>For the period 2025-02-01 to 2025-02-28</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Sales Revenue</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="10" t="n">
         <v>12876000</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="10" t="n">
         <v>11630835.22</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="12" t="n">
         <v>1245164.779999999</v>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Operating Expenses</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="10" t="n">
         <v>685666.67</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Operating Profit</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="12" t="n">
         <v>559498.1099999993</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -513,12 +582,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Net Profit/(Loss)</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="12" t="n">
         <v>559498.1099999993</v>
       </c>
     </row>
@@ -530,210 +599,1036 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Balance Sheet</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>As at 2025-02-28</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>ASSETS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Cash at Bank</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="10" t="n">
         <v>58249420</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Inventory - Raw Material</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>4360286.339999999</v>
+      <c r="B6" s="10" t="n">
+        <v>9965463.34</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Inventory - Packaging</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="10" t="n">
+        <v>22801950</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Inventory - Finished Goods</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>50973912.77000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Land </t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>429290000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>133000000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>66400000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Electrical &amp; Utility Systems</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>14056000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Construction in Progress</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>90334300</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL ASSETS</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>840090321.11</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>LIABILITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Paid-up Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>839530823</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>559498.1099999993</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL EQUITY</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>840090321.11</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL LIABILITIES &amp; EQUITY</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n">
+        <v>840090321.11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:F92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>Note 1</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="17" t="inlineStr"/>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sales Revenue</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="n"/>
+      <c r="E3" s="19" t="n">
+        <v>12876000</v>
+      </c>
+      <c r="F3" s="19" t="n">
+        <v>12876000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Note 2</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="17" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cost of Goods Sold</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="19" t="n">
+        <v>5605177.44</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>5605177.44</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Note 3</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>SG&amp;A Expenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" s="17" t="inlineStr"/>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Marketing &amp; Advertising</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n">
+        <v>84000</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Depreciation Expenses - SG&amp;A</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n">
+        <v>601666.67</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>601666.67</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Note 4</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortization</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="17" t="inlineStr"/>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Depreciation Expenses - COGS</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n">
+        <v>343758.33</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>343758.33</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Depreciation Expenses - SG&amp;A</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n">
+        <v>601666.67</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>601666.67</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Note 5</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="17" t="inlineStr"/>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Interest Income</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Note 11</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Cash and Cash Equivalents</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" s="17" t="inlineStr"/>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cash in hand</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cash at Bank</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n">
+        <v>58249420</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>58249420</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Note 12</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" s="17" t="inlineStr"/>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="19" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Note 13</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" s="17" t="inlineStr"/>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Inventory - Raw Material</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>5605177</v>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>4360286.34</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>9965463.34</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Inventory - Packaging</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>7899300</v>
+      </c>
+      <c r="E43" s="19" t="n">
         <v>14902650</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Inventory - Finished Goods</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>16512266.77</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Land </t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
+      <c r="F43" s="19" t="n">
+        <v>22801950</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Work-in-progress</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="n"/>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="19" t="n"/>
+    </row>
+    <row r="45">
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Inventory - Finished Goods</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>34461646</v>
+      </c>
+      <c r="E45" s="19" t="n">
+        <v>16512266.77000001</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>50973912.77000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>Note 14</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>Advance Payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" s="17" t="inlineStr"/>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Advanced Payments</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="n"/>
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="19" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>Note 15</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>Deferred Preliminary Expenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" s="17" t="inlineStr"/>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Deferred Preliminary Expenses</t>
+        </is>
+      </c>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="19" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>Note 16</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>Property, Plant and Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" s="17" t="inlineStr"/>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Land</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="n">
+        <v>219000000</v>
+      </c>
+      <c r="E63" s="19" t="n">
         <v>210290000</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>554166.67</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>343758.33</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Electrical &amp; Utility Systems</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
+      <c r="F63" s="19" t="n">
+        <v>429290000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="n">
+        <v>133000000</v>
+      </c>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="19" t="n">
+        <v>133000000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="D65" s="19" t="n">
+        <v>66400000</v>
+      </c>
+      <c r="E65" s="19" t="n"/>
+      <c r="F65" s="19" t="n">
+        <v>66400000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="n"/>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="19" t="n"/>
+    </row>
+    <row r="67">
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Electrical &amp; Utility Systems</t>
+        </is>
+      </c>
+      <c r="D67" s="19" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="E67" s="19" t="n">
         <v>6856000</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Electrical &amp; Utility Systems</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>47500</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Construction in Progress</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
+      <c r="F67" s="19" t="n">
+        <v>14056000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Construction in Progress</t>
+        </is>
+      </c>
+      <c r="D68" s="19" t="n"/>
+      <c r="E68" s="19" t="n">
         <v>90334300</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL ASSETS</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>400559498.11</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>LIABILITIES</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL LIABILITIES</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="F68" s="19" t="n">
+        <v>90334300</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Motor Vehicles</t>
+        </is>
+      </c>
+      <c r="D69" s="19" t="n"/>
+      <c r="E69" s="19" t="n"/>
+      <c r="F69" s="19" t="n"/>
+    </row>
+    <row r="70">
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Less: Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="D70" s="19" t="n"/>
+      <c r="E70" s="19" t="n"/>
+      <c r="F70" s="19" t="n">
+        <v>-34980725</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>Note 17</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
         <is>
           <t>Paid-up Capital</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+    </row>
+    <row r="75">
+      <c r="C75" s="17" t="inlineStr"/>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Paid-up Capital</t>
+        </is>
+      </c>
+      <c r="D76" s="19" t="n">
+        <v>439530823</v>
+      </c>
+      <c r="E76" s="19" t="n">
         <v>400000000</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="F76" s="19" t="n">
+        <v>839530823</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>Note 18</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
         <is>
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>559498.1099999993</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL EQUITY</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>400559498.11</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL LIABILITIES &amp; EQUITY</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>400559498.11</v>
-      </c>
+    </row>
+    <row r="81">
+      <c r="C81" s="17" t="inlineStr"/>
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E81" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F81" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Retained Earnings</t>
+        </is>
+      </c>
+      <c r="D82" s="19" t="n"/>
+      <c r="E82" s="19" t="n"/>
+      <c r="F82" s="19" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>Note 19</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" s="17" t="inlineStr"/>
+      <c r="D87" s="17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E87" s="17" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accounts Payable</t>
+        </is>
+      </c>
+      <c r="D88" s="19" t="n"/>
+      <c r="E88" s="19" t="n"/>
+      <c r="F88" s="19" t="n"/>
+    </row>
+    <row r="89">
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Short-term Loans</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="n"/>
+      <c r="E89" s="19" t="n"/>
+      <c r="F89" s="19" t="n"/>
+    </row>
+    <row r="90">
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Utility Bills</t>
+        </is>
+      </c>
+      <c r="D90" s="19" t="n"/>
+      <c r="E90" s="19" t="n"/>
+      <c r="F90" s="19" t="n"/>
+    </row>
+    <row r="91">
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Wages Payable</t>
+        </is>
+      </c>
+      <c r="D91" s="19" t="n"/>
+      <c r="E91" s="19" t="n"/>
+      <c r="F91" s="19" t="n"/>
+    </row>
+    <row r="92">
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bank Loan</t>
+        </is>
+      </c>
+      <c r="D92" s="19" t="n"/>
+      <c r="E92" s="19" t="n"/>
+      <c r="F92" s="19" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
